--- a/out/MLP_Base_repeat_3_000008.xlsx
+++ b/out/MLP_Base_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.037571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001601620847210288</v>
+        <v>-0.0001406177009765524</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1839954733805417</v>
+        <v>-0.1615427303031176</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1842915000846297</v>
+        <v>-0.161804835695005</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4885382293528835</v>
+        <v>0.4368418120883298</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.793722969911152</v>
+        <v>0.7127180552363491</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03480824626989869</v>
+        <v>0.03112488739376818</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3740175641555025</v>
+        <v>0.337424834738658</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0610416757332908</v>
+        <v>0.0545825759020717</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4612813099715267</v>
+        <v>0.4154546388544033</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07415842705125264</v>
+        <v>0.06631138356995801</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.548551047677835</v>
+        <v>0.4934896365311984</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01962434286484083</v>
+        <v>0.01754748852435274</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5135460013109557</v>
+        <v>0.462188898311944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01090248840128569</v>
+        <v>0.009748307293672601</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.037571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5157079711776255</v>
+        <v>0.4641215731132007</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02290712784183181</v>
+        <v>0.0204832806673934</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5506337667671405</v>
+        <v>0.4953518032202523</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008996910249529659</v>
+        <v>0.00804379530719415</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5456999484909463</v>
+        <v>0.4909395134815944</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006404858962304139</v>
+        <v>0.005726959454181017</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5495107314154676</v>
+        <v>0.4943467978864345</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002517961847455115</v>
+        <v>0.002251815172481378</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5481364400030019</v>
+        <v>0.4931172814345592</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001426972832151797</v>
+        <v>0.001275914341784869</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5484711374126998</v>
+        <v>0.4934159798817881</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005410816922670006</v>
+        <v>0.0004823632307329145</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5481236405726876</v>
+        <v>0.4931049431740632</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002504228228725519</v>
+        <v>0.0002239997722305638</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5480841177950769</v>
+        <v>0.4930690576121218</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.864973414506104e-05</v>
+        <v>7.896183061281334e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5480104861893319</v>
+        <v>0.49300278940305</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5479667468382041</v>
+        <v>0.4929633540933177</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.547961725243585</v>
+        <v>0.4929583347326247</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5479578158672361</v>
+        <v>0.4929542799397891</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5479555649395045</v>
+        <v>0.4929516625363703</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5479499732794962</v>
+        <v>0.4929461452943806</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5479436492854883</v>
+        <v>0.4929398213003727</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5479382814969099</v>
+        <v>0.4929344535117943</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5479383182454016</v>
+        <v>0.492934490260286</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5479384284908771</v>
+        <v>0.4929346005057615</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5479385019878608</v>
+        <v>0.4929346740027452</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5479386857303199</v>
+        <v>0.4929348577452043</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5479402291669764</v>
+        <v>0.4929364011818608</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5479416991066495</v>
+        <v>0.4929378711215339</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5479429485553715</v>
+        <v>0.4929391205702559</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5479443082495687</v>
+        <v>0.4929404802644532</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5479421033400595</v>
+        <v>0.4929382753549439</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5479416991066495</v>
+        <v>0.4929378711215339</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5479408538913375</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5479414051187148</v>
+        <v>0.4929375771335992</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5479410743822883</v>
+        <v>0.4929372463971728</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5479407803943539</v>
+        <v>0.4929369524092383</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5479408538913375</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5479404129094356</v>
+        <v>0.49293658492432</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.54794030266396</v>
+        <v>0.4929364746788444</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5479402659154683</v>
+        <v>0.4929364379303527</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5479404129094356</v>
+        <v>0.49293658492432</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.037571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5479399351790419</v>
+        <v>0.4929361071939263</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.637571854792519</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5479408906398292</v>
+        <v>0.4929370626547137</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5479408538913375</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5479405231549112</v>
+        <v>0.4929366951697955</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.547940964136813</v>
+        <v>0.4929371361516975</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5479403394124519</v>
+        <v>0.4929365114273364</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5479401556699928</v>
+        <v>0.4929363276848772</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5479397514365828</v>
+        <v>0.4929359234514672</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5479389062212708</v>
+        <v>0.4929350782361552</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5479388694727791</v>
+        <v>0.4929350414876635</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5479390164667464</v>
+        <v>0.4929351884816308</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5479389429697628</v>
+        <v>0.4929351149846471</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5479390164667464</v>
+        <v>0.4929351884816308</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5479390532152383</v>
+        <v>0.4929352252301227</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5479389429697628</v>
+        <v>0.4929351149846471</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5479393839516646</v>
+        <v>0.4929355559665491</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5479392737061891</v>
+        <v>0.4929354457210736</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5479392369576972</v>
+        <v>0.4929354089725816</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5479391634607136</v>
+        <v>0.492935335475598</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5479391267122219</v>
+        <v>0.4929352987271063</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5479389062212708</v>
+        <v>0.4929350782361552</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5479388327242872</v>
+        <v>0.4929350047391716</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5479387592273035</v>
+        <v>0.492934931242188</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5479387959757955</v>
+        <v>0.4929349679906799</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5479386857303199</v>
+        <v>0.4929348577452043</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5479387959757955</v>
+        <v>0.4929349679906799</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.637571854792519</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.54793908996373</v>
+        <v>0.4929352619786144</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_3_000008.xlsx
+++ b/out/MLP_Base_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.4739754264574855</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432804</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001601620847210288</v>
+        <v>-0.0001236526594031602</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1839954733805417</v>
+        <v>-0.142053155971807</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1841556354652627</v>
+        <v>-0.1421768086312101</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1842915000846297</v>
+        <v>-0.1422693204753968</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4885382293528835</v>
+        <v>0.3326515229919785</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.793722969911152</v>
+        <v>0.5236724286139863</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03480824626989869</v>
+        <v>0.02370131458475573</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3740175641555025</v>
+        <v>0.2378899985710727</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0610416757332908</v>
+        <v>0.04156403024336813</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4612813099715267</v>
+        <v>0.2973090185364634</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07415842705125264</v>
+        <v>0.05049569985920822</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.548551047677835</v>
+        <v>0.3567321765081913</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01962434286484083</v>
+        <v>0.01336242736246978</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5135460013109557</v>
+        <v>0.332896861735163</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01090248840128569</v>
+        <v>0.007421968322479148</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.037571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5157079711776255</v>
+        <v>0.3343673750584216</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02290712784183181</v>
+        <v>0.01559706363615105</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5506337667671405</v>
+        <v>0.3581489157994154</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008996910249529659</v>
+        <v>0.006124243612655672</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5456999484909463</v>
+        <v>0.3547876387027283</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006404858962304139</v>
+        <v>0.004360810827123729</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5495107314154676</v>
+        <v>0.3573812513065776</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002517961847455115</v>
+        <v>0.001712732366539677</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.637571854792519</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5481364400030019</v>
+        <v>0.3564438661853045</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001426972832151797</v>
+        <v>0.000970714534716994</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5484711374126998</v>
+        <v>0.3566702032696556</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005410816922670006</v>
+        <v>0.0003661006768954241</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5481236405726876</v>
+        <v>0.3564320852439979</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002504228228725519</v>
+        <v>0.0001689517500597552</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5480841177950769</v>
+        <v>0.3564035505990011</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.864973414506104e-05</v>
+        <v>5.877869825396398e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5480104861893319</v>
+        <v>0.356351716336868</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5479667468382041</v>
+        <v>0.3563202276370739</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.547961725243585</v>
+        <v>0.3563152127442329</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5479578158672361</v>
+        <v>0.3563109398266673</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5479555649395045</v>
+        <v>0.3563077722051025</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5479499732794962</v>
+        <v>0.3563024028781147</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5479436492854883</v>
+        <v>0.3562964101446844</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5479382814969099</v>
+        <v>0.356291042356106</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5479383182454016</v>
+        <v>0.3562910791045977</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5479384284908771</v>
+        <v>0.3562911893500732</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5479385019878608</v>
+        <v>0.3562912628470569</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5479386857303199</v>
+        <v>0.356291446589516</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5479402291669764</v>
+        <v>0.3562929900261725</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5479416991066495</v>
+        <v>0.3562944599658456</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5479429485553715</v>
+        <v>0.3562957094145676</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5479443082495687</v>
+        <v>0.3562970691087649</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5479421033400595</v>
+        <v>0.3562948641992556</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5479416991066495</v>
+        <v>0.3562944599658456</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5479408538913375</v>
+        <v>0.3562936147505336</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5479414051187148</v>
+        <v>0.3562941659779109</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5479410743822883</v>
+        <v>0.3562938352414844</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5479407803943539</v>
+        <v>0.35629354125355</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5479408538913375</v>
+        <v>0.3562936147505336</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5479404129094356</v>
+        <v>0.3562931737686316</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.54794030266396</v>
+        <v>0.3562930635231561</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5479402659154683</v>
+        <v>0.3562930267746644</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5479404129094356</v>
+        <v>0.3562931737686316</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432804</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5479399351790419</v>
+        <v>0.356292696038238</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5479408906398292</v>
+        <v>0.3562936514990253</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5479408538913375</v>
+        <v>0.3562936147505336</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5479405231549112</v>
+        <v>0.3562932840141072</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.547940964136813</v>
+        <v>0.3562937249960091</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5479403394124519</v>
+        <v>0.356293100271648</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5479401556699928</v>
+        <v>0.3562929165291889</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5479397514365828</v>
+        <v>0.3562925122957789</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5479389062212708</v>
+        <v>0.3562916670804669</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5479388694727791</v>
+        <v>0.3562916303319752</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5479390164667464</v>
+        <v>0.3562917773259424</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5479389429697628</v>
+        <v>0.3562917038289588</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5479390164667464</v>
+        <v>0.3562917773259424</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5479390532152383</v>
+        <v>0.3562918140744343</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5479389429697628</v>
+        <v>0.3562917038289588</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5479393839516646</v>
+        <v>0.3562921448108607</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5479392737061891</v>
+        <v>0.3562920345653852</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5479392369576972</v>
+        <v>0.3562919978168932</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5479391634607136</v>
+        <v>0.3562919243199096</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5479391267122219</v>
+        <v>0.3562918875714179</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5479389062212708</v>
+        <v>0.3562916670804669</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5479388327242872</v>
+        <v>0.3562915935834832</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5479387592273035</v>
+        <v>0.3562915200864996</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5479387959757955</v>
+        <v>0.3562915568349915</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5479386857303199</v>
+        <v>0.356291446589516</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5479387959757955</v>
+        <v>0.3562915568349915</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.54793908996373</v>
+        <v>0.356291850822926</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_3_000008.xlsx
+++ b/out/MLP_Base_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4594370722770691</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4739754264574855</v>
+        <v>-0.3000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5090165734291077</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8369524225432804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5698158740997314</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.762906414714871</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5877422094345093</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5191801786422729</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.478717178106308</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4735117256641388</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.414955561799899</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.432117760181427</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4512090682983398</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4333424270153046</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.457881361246109</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4395781457424164</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4432102739810944</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4332852065563202</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4900640249252319</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4407097101211548</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4134935438632965</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4145794808864594</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4189552962779999</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.415922999382019</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4037850499153137</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4180744886398315</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4091868996620178</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4396397471427917</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4157599806785583</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4145278334617615</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4060209095478058</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4148237109184265</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4240346550941467</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4444938004016876</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.553326427936554</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4589086472988129</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4606396853923798</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.414955561799899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4510947167873383</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.414955561799899</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4235277771949768</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4615001976490021</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4170953035354614</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4159881472587585</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4816017150878906</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4862392842769623</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4828756749629974</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5236334204673767</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.03695242254328</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5841489434242249</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5808678865432739</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.036952422543281</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001236526594031602</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.142053155971807</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4823762476444244</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.03695242254328</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5478678941726685</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.448137640953064</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4807941019535065</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4465486705303192</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4489567577838898</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4405929744243622</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4907576441764832</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.460240364074707</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4758225083351135</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.463222324848175</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4650251865386963</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.4951085448265076</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1421768086312101</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5566176772117615</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1422693204753968</v>
+        <v>-0.1376344013159375</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3326515229919785</v>
+        <v>0.3554947708209639</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4774006903171539</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.03695242254328</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5236724286139863</v>
+        <v>0.5740382177826248</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02370131458475573</v>
+        <v>0.025328964369027</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5155771970748901</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.03695242254328</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2378899985710727</v>
+        <v>0.2686306087510248</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04156403024336813</v>
+        <v>0.04441837339033328</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.551102340221405</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2973090185364634</v>
+        <v>0.3321299382990864</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05049569985920822</v>
+        <v>0.05396276611445282</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4862737953662872</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3567321765081913</v>
+        <v>0.3956334948545841</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01336242736246978</v>
+        <v>0.01427989996163661</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4329938590526581</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.332896861735163</v>
+        <v>0.3701613385110921</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007421968322479148</v>
+        <v>0.007932288068407249</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.603473961353302</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.03695242254328</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3343673750584216</v>
+        <v>0.3717331976147809</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01559706363615105</v>
+        <v>0.01666799420591247</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5851943492889404</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3581489157994154</v>
+        <v>0.3971475533655095</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006124243612655672</v>
+        <v>0.006545697233917116</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5642692446708679</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.036952422543281</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3547876387027283</v>
+        <v>0.3935558483936361</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004360810827123729</v>
+        <v>0.004659224605508718</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4832708537578583</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.03695242254328</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3573812513065776</v>
+        <v>0.3963275969621339</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001712732366539677</v>
+        <v>0.001830868900839244</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5214447379112244</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3564438661853045</v>
+        <v>0.3953261126042101</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.000970714534716994</v>
+        <v>0.001036995300898401</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4614565372467041</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3566702032696556</v>
+        <v>0.3955683482724533</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003661006768954241</v>
+        <v>0.000391936799970422</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4526546597480774</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3564320852439979</v>
+        <v>0.395314026095225</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001689517500597552</v>
+        <v>0.0001810623149373331</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4183099567890167</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3564035505990011</v>
+        <v>0.3952838580791641</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.877869825396398e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4387372136116028</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.356351716336868</v>
+        <v>0.3952287831005959</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.407943006636009e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4572113752365112</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3563202276370739</v>
+        <v>0.3951956392293857</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.539715033180046e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4440917074680328</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3563152127442329</v>
+        <v>0.3951906235919029</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4702574610710144</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3563109398266673</v>
+        <v>0.3951864233825805</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4033364653587341</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3563077722051025</v>
+        <v>0.3951834395034748</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4203239381313324</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3563024028781147</v>
+        <v>0.3951779957584685</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4339316189289093</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3562964101446844</v>
+        <v>0.3951720030250382</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4531751275062561</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.356291042356106</v>
+        <v>0.3951666352364598</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4617016911506653</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3562910791045977</v>
+        <v>0.3951666719849515</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4597137272357941</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3562911893500732</v>
+        <v>0.395166782230427</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4347632825374603</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3562912628470569</v>
+        <v>0.3951668557274106</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5076739192008972</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.03695242254328</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.356291446589516</v>
+        <v>0.3951670394698698</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5856564044952393</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.036952422543281</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3562929900261725</v>
+        <v>0.3951685829065263</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4069779217243195</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3562944599658456</v>
+        <v>0.3951700528461994</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3803132176399231</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3562957094145676</v>
+        <v>0.3951713022949214</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9108620882034302</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.03695242254328</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3562970691087649</v>
+        <v>0.3951726619891187</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6440477967262268</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3562948641992556</v>
+        <v>0.3951704570796094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6863985657691956</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3562944599658456</v>
+        <v>0.3951700528461994</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.63639897108078</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3562936147505336</v>
+        <v>0.3951692076308874</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5402810573577881</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3562941659779109</v>
+        <v>0.3951697588582647</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.5018624067306519</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.762906414714871</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3562938352414844</v>
+        <v>0.3951694281218383</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5274801254272461</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.35629354125355</v>
+        <v>0.3951691341339038</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4924672245979309</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3562936147505336</v>
+        <v>0.3951692076308874</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.466826856136322</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3562931737686316</v>
+        <v>0.3951687666489854</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4556361734867096</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3562930635231561</v>
+        <v>0.3951686564035099</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4754080176353455</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3562930267746644</v>
+        <v>0.3951686196550182</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4538488984107971</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3562931737686316</v>
+        <v>0.3951687666489854</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.6451951265335083</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8369524225432804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.356292696038238</v>
+        <v>0.3951682889185918</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6914400458335876</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3562936514990253</v>
+        <v>0.3951692443793791</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.5301562547683716</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3562936147505336</v>
+        <v>0.3951692076308874</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5136798620223999</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3562932840141072</v>
+        <v>0.395168876894461</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4768436253070831</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3562937249960091</v>
+        <v>0.3951693178763629</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4725446999073029</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.356293100271648</v>
+        <v>0.3951686931520018</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4759776294231415</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3562929165291889</v>
+        <v>0.3951685094095427</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.474252462387085</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3562925122957789</v>
+        <v>0.3951681051761327</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4803984463214874</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3562916670804669</v>
+        <v>0.3951672599608206</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4774802923202515</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3562916303319752</v>
+        <v>0.395167223212329</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4750239849090576</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3562917773259424</v>
+        <v>0.3951673702062962</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4582063853740692</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3562917038289588</v>
+        <v>0.3951672967093126</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5605464577674866</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3562917773259424</v>
+        <v>0.3951673702062962</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4529811143875122</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.03695242254328</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3562918140744343</v>
+        <v>0.3951674069547881</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5292482376098633</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3562917038289588</v>
+        <v>0.3951672967093126</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4342238903045654</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3562921448108607</v>
+        <v>0.3951677376912145</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4558862149715424</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.414955561799899</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3562920345653852</v>
+        <v>0.395167627445739</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4119559824466705</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3562919978168932</v>
+        <v>0.3951675906972471</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4315040111541748</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3562919243199096</v>
+        <v>0.3951675172002634</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4176936447620392</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3562918875714179</v>
+        <v>0.3951674804517717</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4030560851097107</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3562916670804669</v>
+        <v>0.3951672599608206</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.448728621006012</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3562915935834832</v>
+        <v>0.395167186463837</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4248898029327393</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3562915200864996</v>
+        <v>0.3951671129668534</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4163487553596497</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3562915568349915</v>
+        <v>0.3951671497153453</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4572120308876038</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.356291446589516</v>
+        <v>0.3951670394698698</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.5199148058891296</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.03695242254328</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3562915568349915</v>
+        <v>0.3951671497153453</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5101801753044128</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.762906414714871</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.356291850822926</v>
+        <v>0.3951674437032798</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_3_000008.xlsx
+++ b/out/MLP_Base_repeat_3_000008.xlsx
@@ -73289,7 +73289,7 @@
         <v>0.63639897108078</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0.3951692076308874</v>
@@ -74084,7 +74084,7 @@
         <v>0.5402810573577881</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0.3951697588582647</v>
@@ -74879,7 +74879,7 @@
         <v>0.5018624067306519</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
         <v>0.3951694281218383</v>
@@ -75674,7 +75674,7 @@
         <v>0.5274801254272461</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0.3951691341339038</v>
@@ -76469,7 +76469,7 @@
         <v>0.4924672245979309</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0.3951692076308874</v>
@@ -80444,7 +80444,7 @@
         <v>0.6451951265335083</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0.3951682889185918</v>
@@ -81239,7 +81239,7 @@
         <v>0.6914400458335876</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0.3951692443793791</v>
@@ -82034,7 +82034,7 @@
         <v>0.5301562547683716</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0.3951692076308874</v>
@@ -82829,7 +82829,7 @@
         <v>0.5136798620223999</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0.395168876894461</v>
@@ -83624,7 +83624,7 @@
         <v>0.4768436253070831</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
         <v>0.3951693178763629</v>
@@ -84419,7 +84419,7 @@
         <v>0.4725446999073029</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0.3951686931520018</v>
@@ -89984,7 +89984,7 @@
         <v>0.5605464577674866</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
         <v>0.3951673702062962</v>
@@ -90779,7 +90779,7 @@
         <v>0.4529811143875122</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
         <v>0.3951674069547881</v>
@@ -91574,7 +91574,7 @@
         <v>0.5292482376098633</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
         <v>0.3951672967093126</v>
@@ -92369,7 +92369,7 @@
         <v>0.4342238903045654</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0.3951677376912145</v>
@@ -93164,7 +93164,7 @@
         <v>0.4558862149715424</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0.395167627445739</v>
